--- a/test_author_shares_2025_baseline.xlsx
+++ b/test_author_shares_2025_baseline.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="289">
   <si>
     <t xml:space="preserve">ARSTALL</t>
   </si>
@@ -108,313 +108,715 @@
     <t xml:space="preserve">2025</t>
   </si>
   <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019a9c5b3008-2195a490-0539-47fa-a483-5b8de0df81e5</t>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019c70bb7fa2-dc6ffa3b-5846-4bbd-86ed-71b006651741</t>
   </si>
   <si>
     <t xml:space="preserve">AcademicChapter</t>
   </si>
   <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/publisher/86C28E21-4067-412B-9BD2-525EFD20899B/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publisher</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">LevelOne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/467212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UHI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">310000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.32.4.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/184.32.4.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tor Straume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kapittel_populærvitskapleg_bok180226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019d24e98ea7-d4b15a1b-7609-4543-a940-62bbb4192eee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AcademicArticle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/01043000-407F-4729-B41C-CBEBAC9B87C3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speki. Nordisk pedagogisk-filosofisk tidsskrift</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/19990</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">310100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.34.5.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/185.34.5.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elin Holmstrøm Frøshaug</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On Education and Why</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198ad2c5d9b-a550f8f2-e9db-4dcd-ad14-c6ce3303c116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/publisher/DA831BBC-DD1C-4E06-ACA0-48DE8046FB26/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/1261362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">217.53.2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/217.53.2.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hannah Tischmann</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Om funksjonen av klasse i Zeshan Shakars De kaller meg ulven (2022) og Eva Sapieżyńskas Jeg er ikke polakken din (2022): En postmigrantisk lesning av to samtidsskildringer av arbeidsinnvandring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019efe73c6e1-aef0250e-1ada-4b31-866d-e7037ab64d74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/publisher/DC752087-7122-4D3A-9E4F-382AA2F39D2C/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/34322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTHER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20754.0.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/20754.0.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torbjørn Kvåle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kapittel i antologi i 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198acf7d7d6-96aa90cd-4f3b-45bc-a593-702fb4264a65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/DB3B99F8-7A72-48FA-8B1E-0AB486CF99F3/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1089-9995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of Geoscience Education (JGE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/1289129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260470</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.12.44.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/184.12.44.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julien Pooya Weihs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploration of troublesome and threshold concepts in cloud microphysics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/797669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.12.24.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/184.12.24.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vegard Gjerde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/52858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helge Drange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019914e303bb-c1269fc4-43f9-45b2-b19d-bd6a465cfe32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/D33E2218-F8FF-4B5C-B058-476B0051A41E/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1945-0265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genetic Testing and Molecular Biomarkers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/1215176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lars-Olav Vågene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-04 - Test (godkjent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019ab23cca15-722b1340-9c7b-4312-8b9a-345898a65534</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/publisher/4EE891ED-1640-4470-AF80-C0D88242023C/2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Publisher</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">LevelOne</t>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/36898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20754.3.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/20754.3.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anders Eivind Bråten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vit kap i antologi på nivå1 med ISBN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20754.2.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/20754.2.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019a97013423-5ebc8ce4-6932-48a9-b026-9dad6317fe4b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/24773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jon Nornes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test kap 1 forfatter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019ab25f06b0-e32ddc55-2081-450c-96ee-46b1583e8bc0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vit kap i antologi som gjøres om til forskningsrappport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019932badbca-53700bdf-7ccf-4791-8b5c-12057e286054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/50561B90-6679-4FCD-BCB0-99E521B18962/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arbeider fra Geografisk Institutt Universitetet i Trondheim # 16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/7278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">320200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1615.20.20.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/1615.20.20.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marit Henningsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demonstrere flytting av oppgave mellom institusjoner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/42557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan E. Garshol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019a9be3b213-b2c59bcf-db07-408b-aba7-36df00246110</t>
   </si>
   <si>
     <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/402581</t>
   </si>
   <si>
-    <t xml:space="preserve">OTHER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20754.2.0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/20754.2.0.0</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hanne Young</t>
   </si>
   <si>
-    <t xml:space="preserve">test vit kap i leksika</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019c70bb7fa2-dc6ffa3b-5846-4bbd-86ed-71b006651741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/publisher/86C28E21-4067-412B-9BD2-525EFD20899B/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/467212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UHI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">310</t>
-  </si>
-  <si>
-    <t xml:space="preserve">310000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.32.4.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/184.32.4.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tor Straume</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kapittel_populærvitskapleg_bok180226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019d24e98ea7-d4b15a1b-7609-4543-a940-62bbb4192eee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AcademicArticle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/01043000-407F-4729-B41C-CBEBAC9B87C3/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Speki. Nordisk pedagogisk-filosofisk tidsskrift</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/19990</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">310100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.34.5.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/185.34.5.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elin Holmstrøm Frøshaug</t>
-  </si>
-  <si>
-    <t xml:space="preserve">On Education and Why</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198ad2c5d9b-a550f8f2-e9db-4dcd-ad14-c6ce3303c116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/publisher/DA831BBC-DD1C-4E06-ACA0-48DE8046FB26/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/1261362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">217.53.2.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/217.53.2.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hannah Tischmann</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Om funksjonen av klasse i Zeshan Shakars De kaller meg ulven (2022) og Eva Sapieżyńskas Jeg er ikke polakken din (2022): En postmigrantisk lesning av to samtidsskildringer av arbeidsinnvandring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019efe73c6e1-aef0250e-1ada-4b31-866d-e7037ab64d74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/publisher/DC752087-7122-4D3A-9E4F-382AA2F39D2C/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/34322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20754.0.0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/20754.0.0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torbjørn Kvåle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kapittel i antologi i 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019ab23cca15-722b1340-9c7b-4312-8b9a-345898a65534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/36898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20754.3.0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/20754.3.0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anders Eivind Bråten</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vit kap i antologi på nivå1 med ISBN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019a97013423-5ebc8ce4-6932-48a9-b026-9dad6317fe4b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/24773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jon Nornes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test kap 1 forfatter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198acf7d7d6-96aa90cd-4f3b-45bc-a593-702fb4264a65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/DB3B99F8-7A72-48FA-8B1E-0AB486CF99F3/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1089-9995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of Geoscience Education (JGE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/1289129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260470</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.12.44.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/184.12.44.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Julien Pooya Weihs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exploration of troublesome and threshold concepts in cloud microphysics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/797669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260250</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.12.24.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/184.12.24.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vegard Gjerde</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/52858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helge Drange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019ab25f06b0-e32ddc55-2081-450c-96ee-46b1583e8bc0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vit kap i antologi som gjøres om til forskningsrappport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019932badbca-53700bdf-7ccf-4791-8b5c-12057e286054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/50561B90-6679-4FCD-BCB0-99E521B18962/2025</t>
+    <t xml:space="preserve">Vitenskapelig kapittel i antologi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019a9702b332-7c58aa60-d4de-4680-93e1-c6559466a802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test 2 forfattere + 2 adresser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019ab26356fb-61bfaf90-52ca-4ddb-96fd-63201ab0b3a4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitenskapelig kapittel i forskningsrapport AEB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019ac49ffc64-26085c55-ce10-4ad1-a6cb-38081636f8ad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/4BEB3958-6998-4545-AE48-54D66A8DCB83/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1353-3452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Science and Engineering Ethics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/1427301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220</t>
+  </si>
+  <si>
+    <t xml:space="preserve">220910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.11.75.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/184.11.75.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gernot Rieder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">After Harm: A Plea for Moral Repair after Algorithms Have Failed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198acf956dd-038318ce-dab4-499a-b651-b30a5422720c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/38DB920C-658C-4FE0-AEF0-638FCB133B30/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frontiers in Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/43258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210630</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194.67.80.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/194.67.80.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May Britt Postholm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expanding the change laboratory and the interventionist researcher's role in teacher education-school collaboration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019a6e4cf9e5-e7a9e1d8-a00d-45a1-ad56-f6e6b3c600f8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/2D4DFFC9-AFBE-403F-B1CA-8615915EC786/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1091-4269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Depression and Anxiety</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LevelTwo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/1118587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">204.20.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/204.20.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiebke Kallweit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My publication</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/01995d0fa683-173c240f-3ca7-4607-893f-e67c7ff35501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/386F0A44-9D2B-4A1F-8FA7-E1E88FA4B8D7/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communications Biology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine learning based on pangenome-wide association studies reveals the impact of host source on the zoonotic potential of closely related bacterial pathogens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198ad01deff-711d3750-ee3b-472c-8938-446bf5c11768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/72D13335-1CE1-4D02-8FB9-23F969D71F18/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nordisk tidsskrift for utdanning og praksis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/612730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingrid Østgaard Buaas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Importance of Subject Knowledge in Physical Education in Grades 1–4: Teachers’ Experiences of Formal and Informal Competence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/01993d95457e-a0c3f1c2-108b-4b97-9779-ff743608ffa9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/F2C3A9C1-875B-4D44-A98F-90AD2EF5DA9B/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0332-7256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Norsk tidsskrift for logopedi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/1800584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kari Tverelv Angelsen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tester avviste artikler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019c8ef8bfa7-ed1e1876-819e-4bcc-ae26-bd16c2d56762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/3CE2F528-98AD-44DD-A684-1CE9A96EF921/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1650-2787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skånska spår - arkeologi längs Västkustbanan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-24 - Test 2 av poeng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019a9781e461-ddf1eace-8a64-4ac8-a878-ab5d28d92fd3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AcademicMonograph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universitetsforlaget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/331868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kristin Dragvik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeg lurer på hvordan NVI-kontrollen blir i NVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198acf9da7f-a3df4282-3216-4068-9873-ee4a209975ac</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/07D42E71-B746-4787-A347-1CC75DCDF51F/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0016-7649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Journal of the Geological Society</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/51984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">260420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">184.12.50.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/184.12.50.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yngve Kristoffersen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Lomonosov Ridge, central Arctic Ocean – the world's longest submarine ridge of continental origin: outline of the history of exploration, morphology, sediment deposition and exhumation of the North American and Central ridge segments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0199c8c3aa09-5b858c9e-c566-4f05-b2f6-36888a153b50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/publisher/517D4F8F-AF83-4062-82FA-254E8A87D7D8/2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test av registrering av konferanseartikkel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198ad19cb44-8fbeec8d-d78d-4b27-bce6-670e680153db</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/50902F91-88E6-44F3-965A-F793D8E87670/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0260-1370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Journal of Lifelong Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/834903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210940</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">194.67.70.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/194.67.70.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siri Christine Kvernmo Næss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finding the silver lining: the transformative power of dating practices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/33582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liselotte Eva Anna Aarsand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198eb25b9bc-9b33e205-c939-45a8-81c8-0f651a37c3cc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/928C73A5-7806-48DE-9E9E-8CBAA568310D/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0066-4677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anthropological Forum: a journal of social anthropology and comparative sociology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/45279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">210830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">185.17.7.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/185.17.7.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siri Steen Selvig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing SSS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019aa5a16dd7-c5ffec31-92e4-4224-8173-e5727998b847</t>
   </si>
   <si>
     <t xml:space="preserve">0029-2001</t>
@@ -423,382 +825,28 @@
     <t xml:space="preserve">Tidsskrift for Den norske legeforening (Tidsskriftet)</t>
   </si>
   <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/42557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jan E. Garshol</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demonstrere flytting av oppgave mellom institusjoner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/7278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">320200</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1615.20.20.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/1615.20.20.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marit Henningsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019a9702b332-7c58aa60-d4de-4680-93e1-c6559466a802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test 2 forfattere + 2 adresser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019a9be3b213-b2c59bcf-db07-408b-aba7-36df00246110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitenskapelig kapittel i antologi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019914e303bb-c1269fc4-43f9-45b2-b19d-bd6a465cfe32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/D33E2218-F8FF-4B5C-B058-476B0051A41E/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1945-0265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genetic Testing and Molecular Biomarkers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/1215176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lars-Olav Vågene</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-04 - Test (godkjent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019ab26356fb-61bfaf90-52ca-4ddb-96fd-63201ab0b3a4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vitenskapelig kapittel i forskningsrapport AEB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019ac49ffc64-26085c55-ce10-4ad1-a6cb-38081636f8ad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/4BEB3958-6998-4545-AE48-54D66A8DCB83/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1353-3452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Science and Engineering Ethics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/1427301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">220910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.11.75.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/184.11.75.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gernot Rieder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">After Harm: A Plea for Moral Repair after Algorithms Have Failed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198acf956dd-038318ce-dab4-499a-b651-b30a5422720c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/38DB920C-658C-4FE0-AEF0-638FCB133B30/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frontiers in Education</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/43258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1150</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210630</t>
-  </si>
-  <si>
-    <t xml:space="preserve">194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">67</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">194.67.80.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/194.67.80.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">May Britt Postholm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expanding the change laboratory and the interventionist researcher's role in teacher education-school collaboration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019a6e4cf9e5-e7a9e1d8-a00d-45a1-ad56-f6e6b3c600f8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/2D4DFFC9-AFBE-403F-B1CA-8615915EC786/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1091-4269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Depression and Anxiety</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LevelTwo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/1118587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">204.20.0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/204.20.0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiebke Kallweit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">My publication</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198ad0b0cf1-9d147d0b-92ac-44c7-80c0-aab5335a565a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/CEB75710-B16D-4E32-8DA8-041470CCAD61/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BMC Psychiatry</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/1279505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210690</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">194.67.40.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/194.67.40.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mojtaba Habibi Asgarabad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network analysis of caffeine use disorder, withdrawal symptoms, and psychiatric symptoms</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198ad1ad857-6ef7920e-2237-434e-a05f-214b40701751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/76CA78CC-DB0F-49C4-8562-0EC2659FB1BD/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1932-4502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Integrative Psychological and Behavioural Science</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/1319518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danyal Farsani</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dynamic Mathematical Processing Through Symbolic, Situational, and Verbal Representations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/01995d0fa683-173c240f-3ca7-4607-893f-e67c7ff35501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/386F0A44-9D2B-4A1F-8FA7-E1E88FA4B8D7/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communications Biology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine learning based on pangenome-wide association studies reveals the impact of host source on the zoonotic potential of closely related bacterial pathogens</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198ad01deff-711d3750-ee3b-472c-8938-446bf5c11768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/72D13335-1CE1-4D02-8FB9-23F969D71F18/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nordisk tidsskrift for utdanning og praksis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/612730</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ingrid Østgaard Buaas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Importance of Subject Knowledge in Physical Education in Grades 1–4: Teachers’ Experiences of Formal and Informal Competence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019a0bcb180e-72b69e5a-918c-40e4-a00a-3f49bcb8c2cb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/4984F4B6-D57E-4F83-BB8B-8B53A774FDDB/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Glossa: a journal of general linguistics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/380084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1130</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">126220</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">186.26.22.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/186.26.22.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bror-Magnus Sviland Strand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/01993d95457e-a0c3f1c2-108b-4b97-9779-ff743608ffa9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/F2C3A9C1-875B-4D44-A98F-90AD2EF5DA9B/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0332-7256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Norsk tidsskrift for logopedi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/1800584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kari Tverelv Angelsen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tester avviste artikler</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019c8ef8bfa7-ed1e1876-819e-4bcc-ae26-bd16c2d56762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/3CE2F528-98AD-44DD-A684-1CE9A96EF921/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1942-7603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Drug Testing and Analysis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-02-24 - Test 2 av poeng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019a9781e461-ddf1eace-8a64-4ac8-a878-ab5d28d92fd3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AcademicMonograph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universitetsforlaget</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/331868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kristin Dragvik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeg lurer på hvordan NVI-kontrollen blir i NVA</t>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/50194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">158.21.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/158.21.0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Karin Nordenstam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test</t>
   </si>
   <si>
     <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019a973c2bbd-87078cbc-aa6b-4d51-ae0d-c4f7613be112</t>
@@ -832,168 +880,6 @@
   </si>
   <si>
     <t xml:space="preserve">Testing testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198ad17a95b-58b397d8-f522-471c-96e9-68590146c968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/publisher/FAE3940D-29AB-45F5-9190-6242B3BB7596/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/561594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anna M Krulatz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frameworks and models for promoting multilingual practices in classroom contexts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198acf9da7f-a3df4282-3216-4068-9873-ee4a209975ac</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/07D42E71-B746-4787-A347-1CC75DCDF51F/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0016-7649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Journal of the Geological Society</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/51984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">260420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">184.12.50.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/184.12.50.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yngve Kristoffersen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Lomonosov Ridge, central Arctic Ocean – the world's longest submarine ridge of continental origin: outline of the history of exploration, morphology, sediment deposition and exhumation of the North American and Central ridge segments</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0199c8c3aa09-5b858c9e-c566-4f05-b2f6-36888a153b50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/publisher/517D4F8F-AF83-4062-82FA-254E8A87D7D8/2017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test av registrering av konferanseartikkel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198ad19cb44-8fbeec8d-d78d-4b27-bce6-670e680153db</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/50902F91-88E6-44F3-965A-F793D8E87670/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0260-1370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Journal of Lifelong Education</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/834903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210940</t>
-  </si>
-  <si>
-    <t xml:space="preserve">70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">194.67.70.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/194.67.70.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siri Christine Kvernmo Næss</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Finding the silver lining: the transformative power of dating practices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/33582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Liselotte Eva Anna Aarsand</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/019aa5a16dd7-c5ffec31-92e4-4224-8173-e5727998b847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/50194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">158.21.0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/158.21.0.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karin Nordenstam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">test</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication/0198eb25b9bc-9b33e205-c939-45a8-81c8-0f651a37c3cc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/publication-channels-v2/serial-publication/928C73A5-7806-48DE-9E9E-8CBAA568310D/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0066-4677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anthropological Forum: a journal of social anthropology and comparative sociology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/person/45279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">210830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">185.17.7.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://api.test.nva.aws.unit.no/cristin/organization/185.17.7.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siri Steen Selvig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testing SSS</t>
   </si>
 </sst>
 </file>
@@ -1200,52 +1086,52 @@
         <v>39</v>
       </c>
       <c r="L2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N2" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="O2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="T2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="U2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="V2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="W2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="X2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z2" t="n">
         <v>0.7</v>
       </c>
       <c r="AA2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB2" t="n">
         <v>1.0</v>
@@ -1262,91 +1148,91 @@
         <v>30</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F3" t="s">
         <v>35</v>
       </c>
       <c r="G3" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="H3" t="s">
         <v>36</v>
       </c>
       <c r="I3" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="J3" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K3" t="s">
         <v>39</v>
       </c>
       <c r="L3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="M3" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="N3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="O3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="Q3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="R3" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="S3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="T3" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="U3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="V3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="W3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="X3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.7</v>
+        <v>1.0</v>
       </c>
       <c r="AA3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.7</v>
+        <v>0.7071</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.7</v>
+        <v>0.7071</v>
       </c>
     </row>
     <row r="4">
@@ -1354,91 +1240,91 @@
         <v>30</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
         <v>35</v>
       </c>
       <c r="G4" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="H4" t="s">
         <v>36</v>
       </c>
       <c r="I4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="J4" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K4" t="s">
         <v>39</v>
       </c>
       <c r="L4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="M4" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="N4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="O4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="P4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="Q4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="R4" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="S4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="T4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="U4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="V4" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="W4" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="X4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.0</v>
+        <v>0.7</v>
       </c>
       <c r="AA4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7071</v>
+        <v>0.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.7071</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
@@ -1446,13 +1332,13 @@
         <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E5" t="s">
         <v>34</v>
@@ -1467,34 +1353,34 @@
         <v>36</v>
       </c>
       <c r="I5" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="J5" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="K5" t="s">
         <v>39</v>
       </c>
       <c r="L5" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="M5" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="N5" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="O5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P5" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="Q5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="R5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S5" t="s">
         <v>87</v>
@@ -1512,16 +1398,16 @@
         <v>90</v>
       </c>
       <c r="X5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z5" t="n">
         <v>0.7</v>
       </c>
       <c r="AA5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB5" t="n">
         <v>1.0</v>
@@ -1541,25 +1427,25 @@
         <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
         <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="G6" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="H6" t="s">
         <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J6" t="s">
         <v>38</v>
@@ -1568,61 +1454,61 @@
         <v>39</v>
       </c>
       <c r="L6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M6" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="N6" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="O6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P6" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
       <c r="Q6" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="R6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="T6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="U6" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="V6" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="W6" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="X6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7</v>
+        <v>1.0</v>
       </c>
       <c r="AA6" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.7</v>
+        <v>0.3753</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.7</v>
+        <v>0.3753</v>
       </c>
     </row>
     <row r="7">
@@ -1630,28 +1516,28 @@
         <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="H7" t="s">
         <v>36</v>
       </c>
       <c r="I7" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="J7" t="s">
         <v>38</v>
@@ -1660,61 +1546,61 @@
         <v>39</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M7" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="N7" t="s">
-        <v>35</v>
+        <v>106</v>
       </c>
       <c r="O7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P7" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="Q7" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="R7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S7" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="T7" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="U7" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="V7" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="W7" t="s">
         <v>103</v>
       </c>
       <c r="X7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.7</v>
+        <v>1.0</v>
       </c>
       <c r="AA7" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.35</v>
+        <v>0.3753</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.35</v>
+        <v>0.3753</v>
       </c>
     </row>
     <row r="8">
@@ -1722,28 +1608,28 @@
         <v>30</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>35</v>
+        <v>93</v>
       </c>
       <c r="G8" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="H8" t="s">
         <v>36</v>
       </c>
       <c r="I8" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="J8" t="s">
         <v>38</v>
@@ -1752,61 +1638,61 @@
         <v>39</v>
       </c>
       <c r="L8" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M8" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="N8" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="O8" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P8" t="s">
-        <v>41</v>
+        <v>98</v>
       </c>
       <c r="Q8" t="s">
-        <v>42</v>
+        <v>99</v>
       </c>
       <c r="R8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S8" t="s">
-        <v>43</v>
+        <v>100</v>
       </c>
       <c r="T8" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="U8" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="V8" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="W8" t="s">
         <v>103</v>
       </c>
       <c r="X8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7</v>
+        <v>1.0</v>
       </c>
       <c r="AA8" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.35</v>
+        <v>0.3753</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.35</v>
+        <v>0.3753</v>
       </c>
     </row>
     <row r="9">
@@ -1814,31 +1700,31 @@
         <v>30</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F9" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="G9" t="s">
-        <v>35</v>
+        <v>116</v>
       </c>
       <c r="H9" t="s">
         <v>36</v>
       </c>
       <c r="I9" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="J9" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="K9" t="s">
         <v>39</v>
@@ -1853,52 +1739,52 @@
         <v>35</v>
       </c>
       <c r="O9" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="P9" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R9" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S9" t="s">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="T9" t="s">
-        <v>44</v>
+        <v>88</v>
       </c>
       <c r="U9" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="V9" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="W9" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="X9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.7</v>
+        <v>1.0</v>
       </c>
       <c r="AA9" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB9" t="n">
         <v>1.0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.7</v>
+        <v>1.0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.7</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="10">
@@ -1906,91 +1792,91 @@
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C10" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="F10" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="H10" t="s">
         <v>36</v>
       </c>
       <c r="I10" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="J10" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="K10" t="s">
         <v>39</v>
       </c>
       <c r="L10" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="M10" t="s">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="N10" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="O10" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="P10" t="s">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="Q10" t="s">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="R10" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S10" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="T10" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="U10" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="V10" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="W10" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="X10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y10" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.0</v>
+        <v>0.7</v>
       </c>
       <c r="AA10" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.3753</v>
+        <v>0.35</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.3753</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="11">
@@ -1998,22 +1884,22 @@
         <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="G11" t="s">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="H11" t="s">
         <v>36</v>
@@ -2022,67 +1908,67 @@
         <v>122</v>
       </c>
       <c r="J11" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="K11" t="s">
         <v>39</v>
       </c>
       <c r="L11" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="M11" t="s">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="N11" t="s">
-        <v>123</v>
+        <v>35</v>
       </c>
       <c r="O11" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="P11" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="Q11" t="s">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="R11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S11" t="s">
+        <v>127</v>
+      </c>
+      <c r="T11" t="s">
+        <v>128</v>
+      </c>
+      <c r="U11" t="s">
         <v>125</v>
       </c>
-      <c r="T11" t="s">
+      <c r="V11" t="s">
+        <v>125</v>
+      </c>
+      <c r="W11" t="s">
         <v>126</v>
       </c>
-      <c r="U11" t="s">
-        <v>127</v>
-      </c>
-      <c r="V11" t="s">
-        <v>127</v>
-      </c>
-      <c r="W11" t="s">
-        <v>120</v>
-      </c>
       <c r="X11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y11" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.0</v>
+        <v>0.7</v>
       </c>
       <c r="AA11" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.3753</v>
+        <v>0.35</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.3753</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="12">
@@ -2090,91 +1976,91 @@
         <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="F12" t="s">
-        <v>110</v>
+        <v>35</v>
       </c>
       <c r="G12" t="s">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="H12" t="s">
         <v>36</v>
       </c>
       <c r="I12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J12" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="K12" t="s">
         <v>39</v>
       </c>
       <c r="L12" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="M12" t="s">
-        <v>113</v>
+        <v>35</v>
       </c>
       <c r="N12" t="s">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="O12" t="s">
-        <v>56</v>
+        <v>86</v>
       </c>
       <c r="P12" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="Q12" t="s">
-        <v>116</v>
+        <v>46</v>
       </c>
       <c r="R12" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S12" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="T12" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="U12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="V12" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="W12" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="X12" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y12" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.0</v>
+        <v>0.7</v>
       </c>
       <c r="AA12" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.3753</v>
+        <v>0.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.3753</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="13">
@@ -2182,13 +2068,13 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C13" t="s">
         <v>32</v>
       </c>
       <c r="D13" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
         <v>34</v>
@@ -2203,10 +2089,10 @@
         <v>36</v>
       </c>
       <c r="I13" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="J13" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="K13" t="s">
         <v>39</v>
@@ -2221,43 +2107,43 @@
         <v>35</v>
       </c>
       <c r="O13" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="P13" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="Q13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R13" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S13" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="T13" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="U13" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="V13" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="W13" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="X13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y13" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z13" t="n">
         <v>0.7</v>
       </c>
       <c r="AA13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB13" t="n">
         <v>1.0</v>
@@ -2274,28 +2160,28 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C14" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D14" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E14" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F14" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="G14" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H14" t="s">
         <v>36</v>
       </c>
       <c r="I14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J14" t="s">
         <v>38</v>
@@ -2304,52 +2190,52 @@
         <v>39</v>
       </c>
       <c r="L14" t="s">
-        <v>35</v>
+        <v>139</v>
       </c>
       <c r="M14" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="N14" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="O14" t="s">
-        <v>40</v>
+        <v>142</v>
       </c>
       <c r="P14" t="s">
-        <v>41</v>
+        <v>143</v>
       </c>
       <c r="Q14" t="s">
-        <v>42</v>
+        <v>143</v>
       </c>
       <c r="R14" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S14" t="s">
-        <v>43</v>
+        <v>144</v>
       </c>
       <c r="T14" t="s">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="U14" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="V14" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="W14" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="X14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y14" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z14" t="n">
         <v>1.0</v>
       </c>
       <c r="AA14" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB14" t="n">
         <v>2.0</v>
@@ -2366,82 +2252,82 @@
         <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E15" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F15" t="s">
-        <v>134</v>
+        <v>35</v>
       </c>
       <c r="G15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="H15" t="s">
         <v>36</v>
       </c>
       <c r="I15" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="J15" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="K15" t="s">
         <v>39</v>
       </c>
       <c r="L15" t="s">
-        <v>140</v>
+        <v>35</v>
       </c>
       <c r="M15" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="N15" t="s">
-        <v>142</v>
+        <v>35</v>
       </c>
       <c r="O15" t="s">
-        <v>143</v>
+        <v>86</v>
       </c>
       <c r="P15" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="Q15" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="R15" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S15" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="T15" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="U15" t="s">
+        <v>149</v>
+      </c>
+      <c r="V15" t="s">
+        <v>149</v>
+      </c>
+      <c r="W15" t="s">
         <v>147</v>
       </c>
-      <c r="V15" t="s">
-        <v>147</v>
-      </c>
-      <c r="W15" t="s">
-        <v>138</v>
-      </c>
       <c r="X15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y15" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z15" t="n">
         <v>1.0</v>
       </c>
       <c r="AA15" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB15" t="n">
         <v>2.0</v>
@@ -2458,13 +2344,13 @@
         <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="E16" t="s">
         <v>34</v>
@@ -2479,10 +2365,10 @@
         <v>36</v>
       </c>
       <c r="I16" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="J16" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="K16" t="s">
         <v>39</v>
@@ -2497,52 +2383,52 @@
         <v>35</v>
       </c>
       <c r="O16" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="P16" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="Q16" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R16" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S16" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="T16" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="U16" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="V16" t="s">
-        <v>106</v>
+        <v>152</v>
       </c>
       <c r="W16" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="X16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y16" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z16" t="n">
         <v>0.7</v>
       </c>
       <c r="AA16" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.6435</v>
+        <v>0.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.6435</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17">
@@ -2550,13 +2436,13 @@
         <v>30</v>
       </c>
       <c r="B17" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C17" t="s">
         <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>121</v>
       </c>
       <c r="E17" t="s">
         <v>34</v>
@@ -2571,10 +2457,10 @@
         <v>36</v>
       </c>
       <c r="I17" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="J17" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="K17" t="s">
         <v>39</v>
@@ -2589,52 +2475,52 @@
         <v>35</v>
       </c>
       <c r="O17" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="P17" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="Q17" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R17" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>127</v>
       </c>
       <c r="T17" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="U17" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="V17" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="W17" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="X17" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y17" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z17" t="n">
         <v>0.7</v>
       </c>
       <c r="AA17" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.7</v>
+        <v>0.6435</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.7</v>
+        <v>0.6435</v>
       </c>
     </row>
     <row r="18">
@@ -2642,31 +2528,31 @@
         <v>30</v>
       </c>
       <c r="B18" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C18" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D18" t="s">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="E18" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="F18" t="s">
-        <v>154</v>
+        <v>35</v>
       </c>
       <c r="G18" t="s">
-        <v>155</v>
+        <v>35</v>
       </c>
       <c r="H18" t="s">
         <v>36</v>
       </c>
       <c r="I18" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="J18" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="K18" t="s">
         <v>39</v>
@@ -2681,52 +2567,52 @@
         <v>35</v>
       </c>
       <c r="O18" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="P18" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="Q18" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R18" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S18" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="T18" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="U18" t="s">
+        <v>125</v>
+      </c>
+      <c r="V18" t="s">
+        <v>125</v>
+      </c>
+      <c r="W18" t="s">
         <v>157</v>
       </c>
-      <c r="V18" t="s">
-        <v>157</v>
-      </c>
-      <c r="W18" t="s">
-        <v>158</v>
-      </c>
       <c r="X18" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y18" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.0</v>
+        <v>0.7</v>
       </c>
       <c r="AA18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB18" t="n">
         <v>1.0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.0</v>
+        <v>0.7</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="19">
@@ -2734,28 +2620,28 @@
         <v>30</v>
       </c>
       <c r="B19" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D19" t="s">
         <v>159</v>
       </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s">
-        <v>80</v>
-      </c>
       <c r="E19" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F19" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="G19" t="s">
-        <v>35</v>
+        <v>161</v>
       </c>
       <c r="H19" t="s">
         <v>36</v>
       </c>
       <c r="I19" t="s">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="J19" t="s">
         <v>38</v>
@@ -2764,61 +2650,61 @@
         <v>39</v>
       </c>
       <c r="L19" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M19" t="s">
-        <v>35</v>
+        <v>163</v>
       </c>
       <c r="N19" t="s">
-        <v>35</v>
+        <v>164</v>
       </c>
       <c r="O19" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P19" t="s">
-        <v>41</v>
+        <v>165</v>
       </c>
       <c r="Q19" t="s">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="R19" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S19" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="T19" t="s">
-        <v>44</v>
+        <v>168</v>
       </c>
       <c r="U19" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="V19" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="W19" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="X19" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y19" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.7</v>
+        <v>1.0</v>
       </c>
       <c r="AA19" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.7</v>
+        <v>0.9192</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.7</v>
+        <v>0.9192</v>
       </c>
     </row>
     <row r="20">
@@ -2826,91 +2712,91 @@
         <v>30</v>
       </c>
       <c r="B20" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C20" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="E20" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
-        <v>163</v>
+        <v>35</v>
       </c>
       <c r="G20" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="H20" t="s">
         <v>36</v>
       </c>
       <c r="I20" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="J20" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K20" t="s">
         <v>39</v>
       </c>
       <c r="L20" t="s">
-        <v>53</v>
+        <v>175</v>
       </c>
       <c r="M20" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="N20" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="O20" t="s">
-        <v>56</v>
+        <v>178</v>
       </c>
       <c r="P20" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="Q20" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="R20" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S20" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="T20" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="U20" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="V20" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="W20" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="X20" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y20" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z20" t="n">
         <v>1.0</v>
       </c>
       <c r="AA20" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0.9192</v>
+        <v>1.0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.9192</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="21">
@@ -2918,91 +2804,91 @@
         <v>30</v>
       </c>
       <c r="B21" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C21" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E21" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="G21" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="H21" t="s">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="I21" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="J21" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K21" t="s">
         <v>39</v>
       </c>
       <c r="L21" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="M21" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="N21" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="O21" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="P21" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="Q21" t="s">
-        <v>183</v>
+        <v>46</v>
       </c>
       <c r="R21" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S21" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="T21" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="U21" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="V21" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="W21" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="X21" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y21" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="AA21" t="s">
-        <v>48</v>
+        <v>104</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.0</v>
+        <v>2.7577</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.0</v>
+        <v>2.7577</v>
       </c>
     </row>
     <row r="22">
@@ -3010,91 +2896,91 @@
         <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="E22" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F22" t="s">
-        <v>190</v>
+        <v>35</v>
       </c>
       <c r="G22" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H22" t="s">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="I22" t="s">
-        <v>193</v>
+        <v>58</v>
       </c>
       <c r="J22" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K22" t="s">
         <v>39</v>
       </c>
       <c r="L22" t="s">
-        <v>194</v>
+        <v>59</v>
       </c>
       <c r="M22" t="s">
-        <v>195</v>
+        <v>41</v>
       </c>
       <c r="N22" t="s">
-        <v>196</v>
+        <v>60</v>
       </c>
       <c r="O22" t="s">
-        <v>197</v>
+        <v>61</v>
       </c>
       <c r="P22" t="s">
-        <v>144</v>
+        <v>62</v>
       </c>
       <c r="Q22" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="R22" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="S22" t="s">
-        <v>198</v>
+        <v>65</v>
       </c>
       <c r="T22" t="s">
-        <v>199</v>
+        <v>66</v>
       </c>
       <c r="U22" t="s">
-        <v>200</v>
+        <v>67</v>
       </c>
       <c r="V22" t="s">
-        <v>200</v>
+        <v>67</v>
       </c>
       <c r="W22" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="X22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y22" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="AA22" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.7577</v>
+        <v>0.3162</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.7577</v>
+        <v>0.3162</v>
       </c>
     </row>
     <row r="23">
@@ -3102,91 +2988,91 @@
         <v>30</v>
       </c>
       <c r="B23" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C23" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D23" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E23" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
         <v>35</v>
       </c>
       <c r="G23" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H23" t="s">
         <v>36</v>
       </c>
       <c r="I23" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J23" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K23" t="s">
         <v>39</v>
       </c>
       <c r="L23" t="s">
+        <v>175</v>
+      </c>
+      <c r="M23" t="s">
+        <v>176</v>
+      </c>
+      <c r="N23" t="s">
+        <v>177</v>
+      </c>
+      <c r="O23" t="s">
         <v>178</v>
       </c>
-      <c r="M23" t="s">
+      <c r="P23" t="s">
         <v>179</v>
       </c>
-      <c r="N23" t="s">
-        <v>206</v>
-      </c>
-      <c r="O23" t="s">
+      <c r="Q23" t="s">
+        <v>180</v>
+      </c>
+      <c r="R23" t="s">
+        <v>46</v>
+      </c>
+      <c r="S23" t="s">
         <v>181</v>
       </c>
-      <c r="P23" t="s">
+      <c r="T23" t="s">
         <v>182</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="U23" t="s">
         <v>207</v>
       </c>
-      <c r="R23" t="s">
-        <v>42</v>
-      </c>
-      <c r="S23" t="s">
+      <c r="V23" t="s">
+        <v>207</v>
+      </c>
+      <c r="W23" t="s">
         <v>208</v>
       </c>
-      <c r="T23" t="s">
-        <v>209</v>
-      </c>
-      <c r="U23" t="s">
-        <v>210</v>
-      </c>
-      <c r="V23" t="s">
-        <v>210</v>
-      </c>
-      <c r="W23" t="s">
-        <v>211</v>
-      </c>
       <c r="X23" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y23" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z23" t="n">
         <v>1.0</v>
       </c>
       <c r="AA23" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC23" t="n">
-        <v>0.65</v>
+        <v>1.0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0.65</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="24">
@@ -3194,91 +3080,91 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
+        <v>209</v>
+      </c>
+      <c r="C24" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" t="s">
+        <v>210</v>
+      </c>
+      <c r="E24" t="s">
+        <v>56</v>
+      </c>
+      <c r="F24" t="s">
+        <v>211</v>
+      </c>
+      <c r="G24" t="s">
         <v>212</v>
-      </c>
-      <c r="C24" t="s">
-        <v>64</v>
-      </c>
-      <c r="D24" t="s">
-        <v>213</v>
-      </c>
-      <c r="E24" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" t="s">
-        <v>214</v>
-      </c>
-      <c r="G24" t="s">
-        <v>215</v>
       </c>
       <c r="H24" t="s">
         <v>36</v>
       </c>
       <c r="I24" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="J24" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K24" t="s">
         <v>39</v>
       </c>
       <c r="L24" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="M24" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="N24" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="O24" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="P24" t="s">
-        <v>182</v>
+        <v>143</v>
       </c>
       <c r="Q24" t="s">
-        <v>183</v>
+        <v>46</v>
       </c>
       <c r="R24" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S24" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="T24" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="U24" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="V24" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="W24" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="X24" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y24" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z24" t="n">
         <v>1.0</v>
       </c>
       <c r="AA24" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="AB24" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.65</v>
+        <v>1.0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0.65</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="25">
@@ -3286,91 +3172,91 @@
         <v>30</v>
       </c>
       <c r="B25" t="s">
+        <v>216</v>
+      </c>
+      <c r="C25" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" t="s">
+        <v>217</v>
+      </c>
+      <c r="E25" t="s">
+        <v>56</v>
+      </c>
+      <c r="F25" t="s">
+        <v>218</v>
+      </c>
+      <c r="G25" t="s">
         <v>219</v>
-      </c>
-      <c r="C25" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" t="s">
-        <v>220</v>
-      </c>
-      <c r="E25" t="s">
-        <v>66</v>
-      </c>
-      <c r="F25" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" t="s">
-        <v>221</v>
       </c>
       <c r="H25" t="s">
         <v>36</v>
       </c>
       <c r="I25" t="s">
-        <v>68</v>
+        <v>117</v>
       </c>
       <c r="J25" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="K25" t="s">
         <v>39</v>
       </c>
       <c r="L25" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="M25" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="N25" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="O25" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="P25" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="Q25" t="s">
-        <v>73</v>
+        <v>46</v>
       </c>
       <c r="R25" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="S25" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="T25" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="U25" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="V25" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="W25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="X25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y25" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z25" t="n">
         <v>1.0</v>
       </c>
       <c r="AA25" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB25" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.3162</v>
+        <v>1.0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.3162</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="26">
@@ -3378,91 +3264,91 @@
         <v>30</v>
       </c>
       <c r="B26" t="s">
+        <v>221</v>
+      </c>
+      <c r="C26" t="s">
+        <v>222</v>
+      </c>
+      <c r="D26" t="s">
+        <v>70</v>
+      </c>
+      <c r="E26" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" t="s">
         <v>223</v>
-      </c>
-      <c r="C26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26" t="s">
-        <v>224</v>
-      </c>
-      <c r="E26" t="s">
-        <v>66</v>
-      </c>
-      <c r="F26" t="s">
-        <v>35</v>
-      </c>
-      <c r="G26" t="s">
-        <v>225</v>
       </c>
       <c r="H26" t="s">
         <v>36</v>
       </c>
       <c r="I26" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="J26" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K26" t="s">
         <v>39</v>
       </c>
       <c r="L26" t="s">
-        <v>178</v>
+        <v>72</v>
       </c>
       <c r="M26" t="s">
-        <v>179</v>
+        <v>73</v>
       </c>
       <c r="N26" t="s">
-        <v>180</v>
+        <v>74</v>
       </c>
       <c r="O26" t="s">
-        <v>181</v>
+        <v>75</v>
       </c>
       <c r="P26" t="s">
-        <v>182</v>
+        <v>76</v>
       </c>
       <c r="Q26" t="s">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="R26" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S26" t="s">
-        <v>184</v>
+        <v>78</v>
       </c>
       <c r="T26" t="s">
-        <v>185</v>
+        <v>79</v>
       </c>
       <c r="U26" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="V26" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="W26" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="X26" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y26" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="AA26" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB26" t="n">
         <v>1.0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="27">
@@ -3470,91 +3356,91 @@
         <v>30</v>
       </c>
       <c r="B27" t="s">
+        <v>227</v>
+      </c>
+      <c r="C27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" t="s">
+        <v>228</v>
+      </c>
+      <c r="E27" t="s">
+        <v>56</v>
+      </c>
+      <c r="F27" t="s">
         <v>229</v>
       </c>
-      <c r="C27" t="s">
-        <v>64</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="G27" t="s">
         <v>230</v>
       </c>
-      <c r="E27" t="s">
-        <v>66</v>
-      </c>
-      <c r="F27" t="s">
-        <v>35</v>
-      </c>
-      <c r="G27" t="s">
+      <c r="H27" t="s">
+        <v>36</v>
+      </c>
+      <c r="I27" t="s">
         <v>231</v>
       </c>
-      <c r="H27" t="s">
-        <v>192</v>
-      </c>
-      <c r="I27" t="s">
-        <v>232</v>
-      </c>
       <c r="J27" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K27" t="s">
         <v>39</v>
       </c>
       <c r="L27" t="s">
+        <v>40</v>
+      </c>
+      <c r="M27" t="s">
+        <v>96</v>
+      </c>
+      <c r="N27" t="s">
+        <v>232</v>
+      </c>
+      <c r="O27" t="s">
+        <v>43</v>
+      </c>
+      <c r="P27" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q27" t="s">
         <v>233</v>
       </c>
-      <c r="M27" t="s">
+      <c r="R27" t="s">
+        <v>46</v>
+      </c>
+      <c r="S27" t="s">
         <v>234</v>
       </c>
-      <c r="N27" t="s">
+      <c r="T27" t="s">
         <v>235</v>
       </c>
-      <c r="O27" t="s">
+      <c r="U27" t="s">
         <v>236</v>
       </c>
-      <c r="P27" t="s">
+      <c r="V27" t="s">
+        <v>236</v>
+      </c>
+      <c r="W27" t="s">
         <v>237</v>
       </c>
-      <c r="Q27" t="s">
-        <v>238</v>
-      </c>
-      <c r="R27" t="s">
-        <v>239</v>
-      </c>
-      <c r="S27" t="s">
-        <v>240</v>
-      </c>
-      <c r="T27" t="s">
-        <v>241</v>
-      </c>
-      <c r="U27" t="s">
-        <v>242</v>
-      </c>
-      <c r="V27" t="s">
-        <v>242</v>
-      </c>
-      <c r="W27" t="s">
-        <v>243</v>
-      </c>
       <c r="X27" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y27" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z27" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB27" t="n">
         <v>3.0</v>
       </c>
-      <c r="AA27" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.0</v>
-      </c>
       <c r="AC27" t="n">
-        <v>2.1213</v>
+        <v>0.7506</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.1213</v>
+        <v>0.7506</v>
       </c>
     </row>
     <row r="28">
@@ -3562,91 +3448,91 @@
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="D28" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E28" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="F28" t="s">
-        <v>246</v>
+        <v>35</v>
       </c>
       <c r="G28" t="s">
-        <v>247</v>
+        <v>35</v>
       </c>
       <c r="H28" t="s">
         <v>36</v>
       </c>
       <c r="I28" t="s">
-        <v>248</v>
+        <v>122</v>
       </c>
       <c r="J28" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="K28" t="s">
         <v>39</v>
       </c>
       <c r="L28" t="s">
-        <v>194</v>
+        <v>35</v>
       </c>
       <c r="M28" t="s">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="N28" t="s">
-        <v>196</v>
+        <v>35</v>
       </c>
       <c r="O28" t="s">
-        <v>197</v>
+        <v>86</v>
       </c>
       <c r="P28" t="s">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="Q28" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R28" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S28" t="s">
-        <v>198</v>
+        <v>127</v>
       </c>
       <c r="T28" t="s">
-        <v>199</v>
+        <v>128</v>
       </c>
       <c r="U28" t="s">
-        <v>249</v>
+        <v>125</v>
       </c>
       <c r="V28" t="s">
-        <v>249</v>
+        <v>125</v>
       </c>
       <c r="W28" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="X28" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y28" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.0</v>
+        <v>0.7</v>
       </c>
       <c r="AA28" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB28" t="n">
         <v>1.0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.0</v>
+        <v>0.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="29">
@@ -3654,28 +3540,28 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C29" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D29" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="E29" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="G29" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="H29" t="s">
         <v>36</v>
       </c>
       <c r="I29" t="s">
-        <v>156</v>
+        <v>245</v>
       </c>
       <c r="J29" t="s">
         <v>38</v>
@@ -3684,61 +3570,61 @@
         <v>39</v>
       </c>
       <c r="L29" t="s">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="M29" t="s">
-        <v>35</v>
+        <v>176</v>
       </c>
       <c r="N29" t="s">
-        <v>35</v>
+        <v>246</v>
       </c>
       <c r="O29" t="s">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="P29" t="s">
-        <v>42</v>
+        <v>179</v>
       </c>
       <c r="Q29" t="s">
-        <v>42</v>
+        <v>247</v>
       </c>
       <c r="R29" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S29" t="s">
-        <v>94</v>
+        <v>248</v>
       </c>
       <c r="T29" t="s">
-        <v>95</v>
+        <v>249</v>
       </c>
       <c r="U29" t="s">
-        <v>157</v>
+        <v>250</v>
       </c>
       <c r="V29" t="s">
-        <v>157</v>
+        <v>250</v>
       </c>
       <c r="W29" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="X29" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y29" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z29" t="n">
         <v>1.0</v>
       </c>
       <c r="AA29" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30">
@@ -3746,91 +3632,91 @@
         <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="C30" t="s">
-        <v>257</v>
+        <v>54</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>242</v>
       </c>
       <c r="E30" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F30" t="s">
-        <v>35</v>
+        <v>243</v>
       </c>
       <c r="G30" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="H30" t="s">
         <v>36</v>
       </c>
       <c r="I30" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="J30" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K30" t="s">
         <v>39</v>
       </c>
       <c r="L30" t="s">
-        <v>82</v>
+        <v>175</v>
       </c>
       <c r="M30" t="s">
-        <v>83</v>
+        <v>176</v>
       </c>
       <c r="N30" t="s">
-        <v>84</v>
+        <v>246</v>
       </c>
       <c r="O30" t="s">
-        <v>85</v>
+        <v>178</v>
       </c>
       <c r="P30" t="s">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="Q30" t="s">
-        <v>41</v>
+        <v>247</v>
       </c>
       <c r="R30" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S30" t="s">
-        <v>87</v>
+        <v>248</v>
       </c>
       <c r="T30" t="s">
-        <v>88</v>
+        <v>249</v>
       </c>
       <c r="U30" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="V30" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="W30" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="X30" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y30" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="AA30" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.0</v>
+        <v>0.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>5.0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31">
@@ -3838,82 +3724,82 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D31" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="E31" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F31" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="G31" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="H31" t="s">
         <v>36</v>
       </c>
       <c r="I31" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="J31" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K31" t="s">
         <v>39</v>
       </c>
       <c r="L31" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="M31" t="s">
-        <v>267</v>
+        <v>176</v>
       </c>
       <c r="N31" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="O31" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="P31" t="s">
-        <v>168</v>
+        <v>260</v>
       </c>
       <c r="Q31" t="s">
-        <v>42</v>
+        <v>261</v>
       </c>
       <c r="R31" t="s">
-        <v>42</v>
+        <v>262</v>
       </c>
       <c r="S31" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="T31" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="U31" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="V31" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="W31" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="X31" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y31" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z31" t="n">
         <v>1.0</v>
       </c>
       <c r="AA31" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AB31" t="n">
         <v>1.0</v>
@@ -3930,61 +3816,61 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C32" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D32" t="s">
-        <v>274</v>
+        <v>136</v>
       </c>
       <c r="E32" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="F32" t="s">
-        <v>35</v>
+        <v>268</v>
       </c>
       <c r="G32" t="s">
-        <v>35</v>
+        <v>269</v>
       </c>
       <c r="H32" t="s">
-        <v>192</v>
+        <v>36</v>
       </c>
       <c r="I32" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="J32" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K32" t="s">
         <v>39</v>
       </c>
       <c r="L32" t="s">
-        <v>178</v>
+        <v>271</v>
       </c>
       <c r="M32" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
       <c r="N32" t="s">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="O32" t="s">
-        <v>181</v>
+        <v>272</v>
       </c>
       <c r="P32" t="s">
-        <v>182</v>
+        <v>273</v>
       </c>
       <c r="Q32" t="s">
-        <v>183</v>
+        <v>46</v>
       </c>
       <c r="R32" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S32" t="s">
-        <v>184</v>
+        <v>274</v>
       </c>
       <c r="T32" t="s">
-        <v>185</v>
+        <v>275</v>
       </c>
       <c r="U32" t="s">
         <v>276</v>
@@ -3996,25 +3882,25 @@
         <v>277</v>
       </c>
       <c r="X32" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y32" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z32" t="n">
         <v>1.0</v>
       </c>
       <c r="AA32" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.9192</v>
+        <v>1.0</v>
       </c>
       <c r="AD32" t="n">
-        <v>0.9192</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="33">
@@ -4025,13 +3911,13 @@
         <v>278</v>
       </c>
       <c r="C33" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="D33" t="s">
         <v>279</v>
       </c>
       <c r="E33" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F33" t="s">
         <v>280</v>
@@ -4046,31 +3932,31 @@
         <v>282</v>
       </c>
       <c r="J33" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="K33" t="s">
         <v>39</v>
       </c>
       <c r="L33" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="M33" t="s">
-        <v>113</v>
+        <v>283</v>
       </c>
       <c r="N33" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O33" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="P33" t="s">
-        <v>115</v>
+        <v>165</v>
       </c>
       <c r="Q33" t="s">
-        <v>284</v>
+        <v>46</v>
       </c>
       <c r="R33" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="S33" t="s">
         <v>285</v>
@@ -4088,484 +3974,24 @@
         <v>288</v>
       </c>
       <c r="X33" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Y33" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="Z33" t="n">
         <v>1.0</v>
       </c>
       <c r="AA33" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0.7506</v>
+        <v>1.0</v>
       </c>
       <c r="AD33" t="n">
-        <v>0.7506</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>30</v>
-      </c>
-      <c r="B34" t="s">
-        <v>289</v>
-      </c>
-      <c r="C34" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" t="s">
-        <v>290</v>
-      </c>
-      <c r="E34" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" t="s">
-        <v>35</v>
-      </c>
-      <c r="G34" t="s">
-        <v>35</v>
-      </c>
-      <c r="H34" t="s">
-        <v>36</v>
-      </c>
-      <c r="I34" t="s">
-        <v>99</v>
-      </c>
-      <c r="J34" t="s">
-        <v>38</v>
-      </c>
-      <c r="K34" t="s">
-        <v>39</v>
-      </c>
-      <c r="L34" t="s">
-        <v>35</v>
-      </c>
-      <c r="M34" t="s">
-        <v>35</v>
-      </c>
-      <c r="N34" t="s">
-        <v>35</v>
-      </c>
-      <c r="O34" t="s">
-        <v>40</v>
-      </c>
-      <c r="P34" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>42</v>
-      </c>
-      <c r="R34" t="s">
-        <v>42</v>
-      </c>
-      <c r="S34" t="s">
-        <v>43</v>
-      </c>
-      <c r="T34" t="s">
-        <v>44</v>
-      </c>
-      <c r="U34" t="s">
-        <v>102</v>
-      </c>
-      <c r="V34" t="s">
-        <v>102</v>
-      </c>
-      <c r="W34" t="s">
-        <v>291</v>
-      </c>
-      <c r="X34" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AA34" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>30</v>
-      </c>
-      <c r="B35" t="s">
-        <v>292</v>
-      </c>
-      <c r="C35" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" t="s">
-        <v>293</v>
-      </c>
-      <c r="E35" t="s">
-        <v>66</v>
-      </c>
-      <c r="F35" t="s">
-        <v>294</v>
-      </c>
-      <c r="G35" t="s">
-        <v>295</v>
-      </c>
-      <c r="H35" t="s">
-        <v>36</v>
-      </c>
-      <c r="I35" t="s">
-        <v>296</v>
-      </c>
-      <c r="J35" t="s">
-        <v>52</v>
-      </c>
-      <c r="K35" t="s">
-        <v>39</v>
-      </c>
-      <c r="L35" t="s">
-        <v>178</v>
-      </c>
-      <c r="M35" t="s">
-        <v>179</v>
-      </c>
-      <c r="N35" t="s">
-        <v>297</v>
-      </c>
-      <c r="O35" t="s">
-        <v>181</v>
-      </c>
-      <c r="P35" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>298</v>
-      </c>
-      <c r="R35" t="s">
-        <v>42</v>
-      </c>
-      <c r="S35" t="s">
-        <v>299</v>
-      </c>
-      <c r="T35" t="s">
-        <v>300</v>
-      </c>
-      <c r="U35" t="s">
-        <v>301</v>
-      </c>
-      <c r="V35" t="s">
-        <v>301</v>
-      </c>
-      <c r="W35" t="s">
-        <v>302</v>
-      </c>
-      <c r="X35" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AA35" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>30</v>
-      </c>
-      <c r="B36" t="s">
-        <v>292</v>
-      </c>
-      <c r="C36" t="s">
-        <v>64</v>
-      </c>
-      <c r="D36" t="s">
-        <v>293</v>
-      </c>
-      <c r="E36" t="s">
-        <v>66</v>
-      </c>
-      <c r="F36" t="s">
-        <v>294</v>
-      </c>
-      <c r="G36" t="s">
-        <v>295</v>
-      </c>
-      <c r="H36" t="s">
-        <v>36</v>
-      </c>
-      <c r="I36" t="s">
-        <v>303</v>
-      </c>
-      <c r="J36" t="s">
-        <v>52</v>
-      </c>
-      <c r="K36" t="s">
-        <v>39</v>
-      </c>
-      <c r="L36" t="s">
-        <v>178</v>
-      </c>
-      <c r="M36" t="s">
-        <v>179</v>
-      </c>
-      <c r="N36" t="s">
-        <v>297</v>
-      </c>
-      <c r="O36" t="s">
-        <v>181</v>
-      </c>
-      <c r="P36" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>298</v>
-      </c>
-      <c r="R36" t="s">
-        <v>42</v>
-      </c>
-      <c r="S36" t="s">
-        <v>299</v>
-      </c>
-      <c r="T36" t="s">
-        <v>300</v>
-      </c>
-      <c r="U36" t="s">
-        <v>304</v>
-      </c>
-      <c r="V36" t="s">
-        <v>304</v>
-      </c>
-      <c r="W36" t="s">
-        <v>302</v>
-      </c>
-      <c r="X36" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AA36" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>30</v>
-      </c>
-      <c r="B37" t="s">
-        <v>305</v>
-      </c>
-      <c r="C37" t="s">
-        <v>64</v>
-      </c>
-      <c r="D37" t="s">
-        <v>133</v>
-      </c>
-      <c r="E37" t="s">
-        <v>66</v>
-      </c>
-      <c r="F37" t="s">
-        <v>134</v>
-      </c>
-      <c r="G37" t="s">
-        <v>135</v>
-      </c>
-      <c r="H37" t="s">
-        <v>36</v>
-      </c>
-      <c r="I37" t="s">
-        <v>306</v>
-      </c>
-      <c r="J37" t="s">
-        <v>52</v>
-      </c>
-      <c r="K37" t="s">
-        <v>39</v>
-      </c>
-      <c r="L37" t="s">
-        <v>307</v>
-      </c>
-      <c r="M37" t="s">
-        <v>35</v>
-      </c>
-      <c r="N37" t="s">
-        <v>35</v>
-      </c>
-      <c r="O37" t="s">
-        <v>308</v>
-      </c>
-      <c r="P37" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>42</v>
-      </c>
-      <c r="R37" t="s">
-        <v>42</v>
-      </c>
-      <c r="S37" t="s">
-        <v>310</v>
-      </c>
-      <c r="T37" t="s">
-        <v>311</v>
-      </c>
-      <c r="U37" t="s">
-        <v>312</v>
-      </c>
-      <c r="V37" t="s">
-        <v>312</v>
-      </c>
-      <c r="W37" t="s">
-        <v>313</v>
-      </c>
-      <c r="X37" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y37" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AA37" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>30</v>
-      </c>
-      <c r="B38" t="s">
-        <v>314</v>
-      </c>
-      <c r="C38" t="s">
-        <v>64</v>
-      </c>
-      <c r="D38" t="s">
-        <v>315</v>
-      </c>
-      <c r="E38" t="s">
-        <v>66</v>
-      </c>
-      <c r="F38" t="s">
-        <v>316</v>
-      </c>
-      <c r="G38" t="s">
-        <v>317</v>
-      </c>
-      <c r="H38" t="s">
-        <v>36</v>
-      </c>
-      <c r="I38" t="s">
-        <v>318</v>
-      </c>
-      <c r="J38" t="s">
-        <v>52</v>
-      </c>
-      <c r="K38" t="s">
-        <v>39</v>
-      </c>
-      <c r="L38" t="s">
-        <v>69</v>
-      </c>
-      <c r="M38" t="s">
-        <v>179</v>
-      </c>
-      <c r="N38" t="s">
-        <v>319</v>
-      </c>
-      <c r="O38" t="s">
-        <v>71</v>
-      </c>
-      <c r="P38" t="s">
-        <v>320</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>321</v>
-      </c>
-      <c r="R38" t="s">
-        <v>322</v>
-      </c>
-      <c r="S38" t="s">
-        <v>323</v>
-      </c>
-      <c r="T38" t="s">
-        <v>324</v>
-      </c>
-      <c r="U38" t="s">
-        <v>325</v>
-      </c>
-      <c r="V38" t="s">
-        <v>325</v>
-      </c>
-      <c r="W38" t="s">
-        <v>326</v>
-      </c>
-      <c r="X38" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AA38" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="AD38" t="n">
         <v>1.0</v>
       </c>
     </row>
